--- a/alumni_data.xlsx
+++ b/alumni_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\nfsu-alumni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E62B724-E8C7-4CB3-BBBE-A4BAD30BBA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F705E60-2358-4B69-B51E-8DF28EDDC6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2362,7 +2362,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>132</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
